--- a/public/documentation/rationalization/Portfolio_Rationalization_Strategy.xlsx
+++ b/public/documentation/rationalization/Portfolio_Rationalization_Strategy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Rationalization Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Overlap Analysis" sheetId="2" r:id="rId2"/>
-    <sheet name="Action Roadmap" sheetId="3" r:id="rId3"/>
+    <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="BI Recommendations" sheetId="2" r:id="rId2"/>
+    <sheet name="ETL Recommendations" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -399,343 +399,872 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:C9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Metric</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Value</v>
+      </c>
+      <c r="C1" t="str">
         <v>Category</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Recommendations</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Assets Impacted</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Potential Cost Savings</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Risk Level</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Strategic Value</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Lineage Integrity</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Consolidate / Merge BI</v>
+        <v>Total Rationalization Recommendations</v>
       </c>
       <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>11</v>
-      </c>
-      <c r="D2" t="str">
-        <v>$145,000 / yr</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Low</v>
+        <v>29</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Portfolio Scope</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Consolidate / Merge ETL</v>
+        <v>BI Rationalization Documents</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="str">
-        <v>$60,000 / yr</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Low</v>
+        <v>21</v>
+      </c>
+      <c r="C3" t="str">
+        <v>BI Modernization</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Decommission / Retire BI</v>
+        <v>ETL Rationalization Documents</v>
       </c>
       <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4" t="str">
-        <v>$95,000 / yr</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Very Low</v>
+        <v>8</v>
+      </c>
+      <c r="C4" t="str">
+        <v>ETL Modernization</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Decommission / Retire ETL</v>
+        <v>Consolidation / Merge Candidates</v>
       </c>
       <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5" t="str">
-        <v>$40,000 / yr</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Very Low</v>
+        <v>6</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Consolidation</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Retain / Modernize BI</v>
+        <v>Decommission / Retire Candidates</v>
       </c>
       <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="E6" t="str">
-        <v>None</v>
-      </c>
-      <c r="F6" t="str">
-        <v>High Core Value</v>
+        <v>7</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Decommission</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Retain / Modernize ETL</v>
+        <v>Retained Core Assets</v>
       </c>
       <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="E7" t="str">
-        <v>None</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Mission Critical Ingestion</v>
+        <v>16</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Retention</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>BI-ETL Connections Mapped</v>
+        <v>Orphan Cascade Candidates</v>
       </c>
       <c r="B8">
-        <v>32</v>
-      </c>
-      <c r="C8">
-        <v>32</v>
-      </c>
-      <c r="E8" t="str">
-        <v>None</v>
-      </c>
-      <c r="G8" t="str">
-        <v>100% Validated</v>
+        <v>1</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Lifecycle Cascade</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Cross-Technology Candidates</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Cross-Platform</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:G22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Overlap Metric</v>
+        <v>Recommendation ID</v>
       </c>
       <c r="B1" t="str">
-        <v>Count</v>
+        <v>Title</v>
       </c>
       <c r="C1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="D1" t="str">
         <v>Domain</v>
       </c>
-      <c r="D1" t="str">
-        <v>Description</v>
+      <c r="E1" t="str">
+        <v>Action</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Overlap %</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Rationale</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Source Metadata Overlaps</v>
-      </c>
-      <c r="B2">
-        <v>18</v>
+        <v>tb_merge_1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Cross Sell &amp; Distribution Revenue Consolidation</v>
       </c>
       <c r="C2" t="str">
-        <v>BI</v>
+        <v>merge-bi</v>
       </c>
       <c r="D2" t="str">
-        <v>Multiple dashboards querying identical tables with redundant schema definitions</v>
+        <v>Distribution</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Consolidate Cross Sell Dashboard into INSURANCE ANALYTICS DASHBOARD.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>84%</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Both workbooks source from identical brokerage sales extracts. Consolidating establishes a single distribution analytics hub.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Logic &amp; Metric Overlaps</v>
-      </c>
-      <c r="B3">
-        <v>12</v>
+        <v>pbi_merge_1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>New Business Lower Quartile &amp; Loss Ratio Consolidation</v>
       </c>
       <c r="C3" t="str">
-        <v>BI</v>
+        <v>merge-bi</v>
       </c>
       <c r="D3" t="str">
-        <v>Duplicated formula and calculated field logic across separate workbooks</v>
+        <v>Claims</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Consolidate into Loss Ratio on Power BI.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>78%</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Both Power BI dashboards analyze agent productivity, retention correlations, and loss ratio performance across broker tiers.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>KPI Overlaps</v>
-      </c>
-      <c r="B4">
-        <v>24</v>
+        <v>pbi_merge_2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Survival Rate &amp; Agent Enablement Consolidation</v>
       </c>
       <c r="C4" t="str">
-        <v>BI</v>
+        <v>merge-bi</v>
       </c>
       <c r="D4" t="str">
-        <v>Identical key performance indicators computed independently</v>
+        <v>Distribution</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Consolidate into New Business (Bottom 25% agents) on Power BI.</v>
+      </c>
+      <c r="F4" t="str">
+        <v>72%</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Both dashboards evaluate broker survival curves, conversion rates, and new business binding volumes across underperforming agent quartiles.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ETL Source Overlaps</v>
-      </c>
-      <c r="B5">
-        <v>14</v>
+        <v>mb2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Cross Sell Analytics Unification</v>
       </c>
       <c r="C5" t="str">
-        <v>ETL</v>
+        <v>merge-bi</v>
       </c>
       <c r="D5" t="str">
-        <v>Multiple workflows reading the same underlying operational Excel files</v>
+        <v>Distribution</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Merge into Cross Sell Dashboard PBIP on Power BI.</v>
+      </c>
+      <c r="F5" t="str">
+        <v>68%</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Tableau and Power BI versions track overlapping policy cross-selling opportunities across multi-line accounts.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ETL Logic Overlaps</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
+        <v>mb4</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Financial Analytics Enterprise Merger</v>
       </c>
       <c r="C6" t="str">
-        <v>ETL</v>
+        <v>merge-bi</v>
       </c>
       <c r="D6" t="str">
-        <v>Duplicate filtering and aggregation logic across disparate workflow files</v>
+        <v>Finance</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Consolidate into Insurance Analytics Dashboard (Power BI).</v>
+      </c>
+      <c r="F6" t="str">
+        <v>64%</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Both workbooks monitor identical enterprise financial metrics (combined ratio, investment yield, expense allocations).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Cross-Technology Overlaps</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
+        <v>pbi_retire_1</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Retire FFQ_Test Report</v>
       </c>
       <c r="C7" t="str">
-        <v>BI &amp; ETL</v>
+        <v>bi-retire</v>
       </c>
       <c r="D7" t="str">
-        <v>Overlaps spanning across Tableau, Power BI, and Alteryx pipelines</v>
+        <v>Underwriting</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Decommission Power BI FFQ_Test report.</v>
+      </c>
+      <c r="F7" t="str">
+        <v>—</v>
+      </c>
+      <c r="G7" t="str">
+        <v>INACTIVE: Experimental rating prototype last accessed 200 days ago (&gt;180 days threshold).</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>pbi_retire_2</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Retire IT Spend Analysis Sample</v>
+      </c>
+      <c r="C8" t="str">
+        <v>bi-retire</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Decommission Power BI IT Spend Analysis report.</v>
+      </c>
+      <c r="F8" t="str">
+        <v>—</v>
+      </c>
+      <c r="G8" t="str">
+        <v>INACTIVE: Departmental IT budget variance workbook last viewed 210 days ago (&gt;180 days threshold).</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>pbi_retire_3</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Retire Sales &amp; Returns Sample v3</v>
+      </c>
+      <c r="C9" t="str">
+        <v>bi-retire</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Decommission Power BI Sales &amp; Returns Sample v3 report.</v>
+      </c>
+      <c r="F9" t="str">
+        <v>—</v>
+      </c>
+      <c r="G9" t="str">
+        <v>INACTIVE: Departmental financial reconciliation and returns report last accessed 240 days ago (&gt;180 days threshold).</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>tb_keep_1</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Keep Benefeciery services_v1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>bi-keep</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Customer</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Retain for continued operation and migration.</v>
+      </c>
+      <c r="F10" t="str">
+        <v>—</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Core customer beneficiary reporting workbook providing SLA compliance and payout metrics.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>tb_keep_2</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Keep Benefeciery_services_Aging_Dashboard</v>
+      </c>
+      <c r="C11" t="str">
+        <v>bi-keep</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Customer</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Retain for continued operation and migration.</v>
+      </c>
+      <c r="F11" t="str">
+        <v>—</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Critical aging review tracking open beneficiary dispute queues and escalation benchmarks.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>tb_keep_3</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Keep Claims - Agent Performance</v>
+      </c>
+      <c r="C12" t="str">
+        <v>bi-keep</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Retain for continued operation and migration.</v>
+      </c>
+      <c r="F12" t="str">
+        <v>—</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Primary agent-level resolution SLA dashboard utilized across regional claims centers.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>tb_keep_4</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Keep Claims - Executive Summary</v>
+      </c>
+      <c r="C13" t="str">
+        <v>bi-keep</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Retain for continued operation and migration.</v>
+      </c>
+      <c r="F13" t="str">
+        <v>—</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Executive portfolio view tracking enterprise incurred claims, loss frequency, and paid amounts.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>tb_keep_5</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Keep Claims - State Performance</v>
+      </c>
+      <c r="C14" t="str">
+        <v>bi-keep</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Retain for continued operation and migration.</v>
+      </c>
+      <c r="F14" t="str">
+        <v>—</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Essential statutory and geographic loss severity dashboard across jurisdictions.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>tb_keep_6</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Keep Sales Insurance</v>
+      </c>
+      <c r="C15" t="str">
+        <v>bi-keep</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Retain for continued operation and migration.</v>
+      </c>
+      <c r="F15" t="str">
+        <v>—</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Commercial broker distribution dashboard tracking account executive quotas.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>tb_keep_7</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Keep Car Insurance Dashboard</v>
+      </c>
+      <c r="C16" t="str">
+        <v>bi-keep</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Underwriting</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Retain for continued operation and migration.</v>
+      </c>
+      <c r="F16" t="str">
+        <v>—</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Core auto underwriting loss frequency and driver demographic risk model.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>tb_keep_8</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Keep Healthcare Claim Analysis Dashboard</v>
+      </c>
+      <c r="C17" t="str">
+        <v>bi-keep</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Retain for continued operation and migration.</v>
+      </c>
+      <c r="F17" t="str">
+        <v>—</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Clinical health claims diagnostic evaluation and benefit cost breakdown.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>bk8</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Keep P&amp;C Claims Dashboard v3</v>
+      </c>
+      <c r="C18" t="str">
+        <v>bi-keep</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Retain for continued operation and migration.</v>
+      </c>
+      <c r="F18" t="str">
+        <v>—</v>
+      </c>
+      <c r="G18" t="str">
+        <v>High-criticality property and casualty loss reserve projection dossier.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>pbi_keep_1</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Keep Bottom 25% Agents</v>
+      </c>
+      <c r="C19" t="str">
+        <v>bi-keep</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Retain for continued operation and migration.</v>
+      </c>
+      <c r="F19" t="str">
+        <v>—</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Lower quartile broker production scorecard for field sales coaching.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>pbi_keep_2</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Keep Jornaya Dashboard PBI</v>
+      </c>
+      <c r="C20" t="str">
+        <v>bi-keep</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Retain for continued operation and migration.</v>
+      </c>
+      <c r="F20" t="str">
+        <v>—</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Lead compliance and consumer journey verification dashboard.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>pbi_keep_3</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Keep Loss Ratio</v>
+      </c>
+      <c r="C21" t="str">
+        <v>bi-keep</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Retain for continued operation and migration.</v>
+      </c>
+      <c r="F21" t="str">
+        <v>—</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Core enterprise loss ratio tracking incurred losses against earned premiums.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>pbi_keep_4</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Keep Revenue Opportunities</v>
+      </c>
+      <c r="C22" t="str">
+        <v>bi-keep</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Retain for continued operation and migration.</v>
+      </c>
+      <c r="F22" t="str">
+        <v>—</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Premium growth opportunity and rate change forecasting model.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:H9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Phase</v>
+        <v>Recommendation ID</v>
       </c>
       <c r="B1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Subtype</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Domain</v>
+      </c>
+      <c r="F1" t="str">
         <v>Action</v>
       </c>
-      <c r="C1" t="str">
-        <v>Duration</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Effort</v>
+      <c r="G1" t="str">
+        <v>Overlap %</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Rationale</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Phase 1: Quick Wins</v>
+        <v>em2</v>
       </c>
       <c r="B2" t="str">
-        <v>Decommission unused test reports (FFQ Test, Test) and obsolete extracts</v>
+        <v>Claims Workflow Consolidation</v>
       </c>
       <c r="C2" t="str">
-        <v>2 Weeks</v>
+        <v>etl-merge</v>
       </c>
       <c r="D2" t="str">
-        <v>Low</v>
+        <v>Consolidation</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Consolidate Workflow_01 into Workflow_03.</v>
+      </c>
+      <c r="G2" t="str">
+        <v>90%</v>
+      </c>
+      <c r="H2" t="str">
+        <v>The workflows share identical data sources and execution frequencies with 90% logic similarity. Consolidating into Workflow_03 eliminates redundant processing.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Phase 2: Consolidation</v>
+        <v>er1</v>
       </c>
       <c r="B3" t="str">
-        <v>Merge Claims Performance &amp; Executive Summary in Tableau</v>
+        <v>Retire Claims_Extract_Volume_v2 (Redundant ETL)</v>
       </c>
       <c r="C3" t="str">
-        <v>4 Weeks</v>
+        <v>etl-retire</v>
       </c>
       <c r="D3" t="str">
-        <v>Medium</v>
+        <v>Subset</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Decommission Claims_Extract_Volume_v2 pipeline.</v>
+      </c>
+      <c r="G3" t="str">
+        <v>96%</v>
+      </c>
+      <c r="H3" t="str">
+        <v>This workflow exhibits identical source, target, transformation, schema, grain, DAG and frequency overlap with Claims_Extract_Volume.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Phase 3: Cross-Tech Merge</v>
+        <v>er2</v>
       </c>
       <c r="B4" t="str">
-        <v>Consolidate Finance and Distribution dashboards across Tableau &amp; Power BI</v>
+        <v>Retire Workflow_04_App</v>
       </c>
       <c r="C4" t="str">
-        <v>6 Weeks</v>
+        <v>etl-retire</v>
       </c>
       <c r="D4" t="str">
-        <v>Medium-High</v>
+        <v>Zombie ETL</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Underwriting</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Decommission inactive workflow.</v>
+      </c>
+      <c r="G4" t="str">
+        <v>—</v>
+      </c>
+      <c r="H4" t="str">
+        <v>INACTIVE: Workflow has been inactive for over 200 days (&gt;180 days threshold). Produces no production deliverables and terminates exclusively in inspection nodes.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Phase 4: ETL Optimization</v>
+        <v>er3</v>
       </c>
       <c r="B5" t="str">
-        <v>Consolidate Alteryx Claims Extract workflows and migrate to Python Delta pipeline</v>
+        <v>Decommission Claims_Extract_Volume (Cross-Technology Parity)</v>
       </c>
       <c r="C5" t="str">
-        <v>8 Weeks</v>
+        <v>etl-retire</v>
       </c>
       <c r="D5" t="str">
-        <v>High</v>
+        <v>Cross-Technology</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Decommission legacy Alteryx workflow Claims_Extract_Volume in favor of modernized claims_processing Python pipeline.</v>
+      </c>
+      <c r="G5" t="str">
+        <v>96%</v>
+      </c>
+      <c r="H5" t="str">
+        <v>CROSS-TECHNOLOGY REPLACEMENT: Alteryx workflow Claims_Extract_Volume has been transpiled into vectorized Python pipeline claims_processing. Both pipelines ingest identical 4 Excel sources and generate identical output marts.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>er4</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Retire Workflow_08 (Orphan Cascade)</v>
+      </c>
+      <c r="C6" t="str">
+        <v>etl-retire</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Orphan Cascade</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Decommission orphaned ETL workflow Workflow_08.</v>
+      </c>
+      <c r="G6" t="str">
+        <v>—</v>
+      </c>
+      <c r="H6" t="str">
+        <v>The associated BI dashboard (Sales &amp; Returns Sample v3) is recommended for Inactive decommissioning. Since Workflow_08 has no downstream consumers beyond this dashboard, the decommissioning decision cascades to Workflow_08.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ek1</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Keep Claims_Extract_Volume</v>
+      </c>
+      <c r="C7" t="str">
+        <v>etl-keep</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Core Pipeline</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Retain Claims_Extract_Volume for migration.</v>
+      </c>
+      <c r="G7" t="str">
+        <v>—</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Retained Alteryx workflow identified for migration and continued operational use.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ek3</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Keep Workflow_02</v>
+      </c>
+      <c r="C8" t="str">
+        <v>etl-keep</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Core Pipeline</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Retain Workflow_02 for migration.</v>
+      </c>
+      <c r="G8" t="str">
+        <v>—</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Retained Alteryx workflow identified for migration and continued operational use.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ek4</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Keep Workflow_03</v>
+      </c>
+      <c r="C9" t="str">
+        <v>etl-keep</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Core Pipeline</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Retain Workflow_03 for migration.</v>
+      </c>
+      <c r="G9" t="str">
+        <v>—</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Retained Alteryx workflow identified for migration and continued operational use.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
   </ignoredErrors>
 </worksheet>
 </file>